--- a/data/trans_dic/IP12B$garganta-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,42; 88,61</t>
+          <t>42,58; 88,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,85; 77,66</t>
+          <t>37,53; 77,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,5; 81,33</t>
+          <t>20,99; 81,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,85; 73,66</t>
+          <t>23,21; 71,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 64,08</t>
+          <t>12,89; 59,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 78,22</t>
+          <t>20,6; 82,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,15; 75,42</t>
+          <t>41,31; 73,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,18; 67,63</t>
+          <t>34,62; 66,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,49; 70,8</t>
+          <t>28,87; 71,79</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,65; 62,14</t>
+          <t>20,92; 64,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,15; 65,11</t>
+          <t>26,7; 64,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,45; 59,64</t>
+          <t>24,46; 59,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,01; 71,57</t>
+          <t>29,9; 68,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 57,67</t>
+          <t>14,2; 56,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,77; 73,36</t>
+          <t>29,29; 71,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,83; 60,56</t>
+          <t>32,57; 62,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,85; 54,21</t>
+          <t>27,28; 55,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,07; 59,87</t>
+          <t>32,61; 59,57</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,19; 70,44</t>
+          <t>28,7; 70,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,19; 75,11</t>
+          <t>26,08; 74,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,84; 84,02</t>
+          <t>40,02; 83,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,24; 66,59</t>
+          <t>13,42; 67,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,71; 78,64</t>
+          <t>41,6; 79,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,72; 58,55</t>
+          <t>18,8; 58,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,98; 62,12</t>
+          <t>26,92; 61,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,22; 73,31</t>
+          <t>43,32; 72,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,43; 63,03</t>
+          <t>33,71; 65,2</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,25; 90,18</t>
+          <t>32,86; 90,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,91; 66,53</t>
+          <t>24,78; 66,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 57,21</t>
+          <t>15,76; 60,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,93; 73,54</t>
+          <t>23,96; 73,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,59; 70,44</t>
+          <t>33,08; 70,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,75; 74,93</t>
+          <t>21,02; 79,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,73; 75,59</t>
+          <t>35,53; 75,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,06; 64,19</t>
+          <t>35,5; 62,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,15; 61,38</t>
+          <t>24,44; 57,21</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,51; 67,85</t>
+          <t>44,01; 68,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,82; 62,53</t>
+          <t>41,34; 61,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,69; 57,21</t>
+          <t>36,39; 58,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,85; 58,92</t>
+          <t>34,77; 57,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,07; 58,52</t>
+          <t>36,72; 57,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,32; 57,36</t>
+          <t>33,47; 57,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,54; 58,98</t>
+          <t>42,59; 59,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,96; 56,64</t>
+          <t>41,8; 56,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,2; 53,8</t>
+          <t>38,53; 53,84</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8553</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10199</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4590</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5493</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3539</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3478</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14046</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13739</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8069</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5212; 10789</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6434; 13302</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1862; 7202</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2736; 8443</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1317; 6111</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1467; 5877</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9926; 17751</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9469; 18216</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4616; 11480</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8988</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8424</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8088</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>13428</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16513</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2531; 7854</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5121; 12295</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4959; 12052</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4827; 11039</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2005; 7975</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4556; 11052</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9199; 17640</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9088; 18376</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>11685; 21344</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6368</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4982</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7377</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2950</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10965</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5894</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9318</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>15948</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>13270</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3644; 9001</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2456; 7061</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4640; 9675</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1111; 5551</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7537; 14319</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2998; 9328</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5647; 12831</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>11927; 19843</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9283; 17953</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4638</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7237</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5157</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5063</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10984</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4344</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9701</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>18221</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9502</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2250; 6168</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3853; 10339</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2267; 8645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2514; 7740</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6983; 14779</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1942; 7301</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6161; 13016</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>13012; 22888</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>5775; 13518</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>24550</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31407</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25548</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29929</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21805</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46267</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>61336</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>47354</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>19310; 29995</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25338; 37976</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20062; 32430</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16241; 26946</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23341; 36335</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16019; 27576</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>38578; 53788</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>52194; 70015</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>39679; 55447</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$garganta-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,58; 88,14</t>
+          <t>42,1; 87,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,53; 77,6</t>
+          <t>37,06; 78,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,99; 81,18</t>
+          <t>23,45; 80,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,21; 71,63</t>
+          <t>23,09; 70,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,89; 59,84</t>
+          <t>13,19; 65,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,6; 82,56</t>
+          <t>14,73; 82,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,31; 73,88</t>
+          <t>41,66; 74,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,62; 66,59</t>
+          <t>33,76; 66,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,87; 71,79</t>
+          <t>27,56; 71,17</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,92; 64,94</t>
+          <t>20,94; 63,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,7; 64,09</t>
+          <t>29,9; 65,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,46; 59,45</t>
+          <t>24,37; 58,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,9; 68,37</t>
+          <t>32,41; 71,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,2; 56,45</t>
+          <t>14,09; 56,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,29; 71,05</t>
+          <t>30,41; 70,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,57; 62,46</t>
+          <t>32,14; 60,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,28; 55,17</t>
+          <t>27,31; 54,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,61; 59,57</t>
+          <t>34,32; 60,16</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 70,89</t>
+          <t>26,62; 69,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,08; 74,99</t>
+          <t>26,57; 75,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,02; 83,46</t>
+          <t>39,25; 83,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 67,06</t>
+          <t>11,73; 66,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,6; 79,04</t>
+          <t>42,06; 77,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 58,51</t>
+          <t>16,63; 55,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,92; 61,17</t>
+          <t>28,94; 61,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,32; 72,07</t>
+          <t>42,61; 71,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,71; 65,2</t>
+          <t>33,82; 64,4</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,86; 90,11</t>
+          <t>32,46; 90,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,78; 66,48</t>
+          <t>23,9; 69,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,76; 60,09</t>
+          <t>16,61; 57,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,96; 73,75</t>
+          <t>23,12; 73,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,08; 70,02</t>
+          <t>31,96; 71,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,02; 79,02</t>
+          <t>22,3; 77,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,53; 75,06</t>
+          <t>36,18; 76,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,5; 62,44</t>
+          <t>37,03; 64,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,44; 57,21</t>
+          <t>24,42; 57,91</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,01; 68,36</t>
+          <t>44,04; 68,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,34; 61,96</t>
+          <t>41,12; 62,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,39; 58,83</t>
+          <t>36,33; 56,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,77; 57,69</t>
+          <t>33,93; 58,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,72; 57,17</t>
+          <t>36,04; 57,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,47; 57,62</t>
+          <t>33,87; 57,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,59; 59,38</t>
+          <t>43,1; 60,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,8; 56,08</t>
+          <t>42,14; 56,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,53; 53,84</t>
+          <t>37,95; 53,78</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5212; 10789</t>
+          <t>5153; 10699</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6434; 13302</t>
+          <t>6353; 13378</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1862; 7202</t>
+          <t>2080; 7108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2736; 8443</t>
+          <t>2722; 8303</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1317; 6111</t>
+          <t>1347; 6652</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1467; 5877</t>
+          <t>1049; 5850</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9926; 17751</t>
+          <t>10010; 17958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9469; 18216</t>
+          <t>9235; 18295</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4616; 11480</t>
+          <t>4407; 11382</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2531; 7854</t>
+          <t>2532; 7662</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5121; 12295</t>
+          <t>5736; 12526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4959; 12052</t>
+          <t>4942; 11949</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4827; 11039</t>
+          <t>5233; 11478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2005; 7975</t>
+          <t>1990; 7952</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4556; 11052</t>
+          <t>4731; 11022</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9199; 17640</t>
+          <t>9076; 17200</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9088; 18376</t>
+          <t>9096; 18222</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11685; 21344</t>
+          <t>12295; 21555</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3644; 9001</t>
+          <t>3380; 8879</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2456; 7061</t>
+          <t>2502; 7111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4640; 9675</t>
+          <t>4550; 9698</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1111; 5551</t>
+          <t>971; 5520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7537; 14319</t>
+          <t>7621; 14076</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2998; 9328</t>
+          <t>2651; 8788</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5647; 12831</t>
+          <t>6069; 12910</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11927; 19843</t>
+          <t>11731; 19743</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9283; 17953</t>
+          <t>9314; 17733</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2250; 6168</t>
+          <t>2222; 6195</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3853; 10339</t>
+          <t>3716; 10818</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2267; 8645</t>
+          <t>2390; 8240</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2514; 7740</t>
+          <t>2426; 7695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6983; 14779</t>
+          <t>6745; 15005</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1942; 7301</t>
+          <t>2060; 7164</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6161; 13016</t>
+          <t>6274; 13229</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13012; 22888</t>
+          <t>13575; 23782</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5775; 13518</t>
+          <t>5769; 13683</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19310; 29995</t>
+          <t>19323; 29890</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25338; 37976</t>
+          <t>25203; 38201</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20062; 32430</t>
+          <t>20027; 31390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16241; 26946</t>
+          <t>15846; 27115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23341; 36335</t>
+          <t>22908; 36394</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16019; 27576</t>
+          <t>16210; 27319</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38578; 53788</t>
+          <t>39041; 54428</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52194; 70015</t>
+          <t>52614; 70406</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39679; 55447</t>
+          <t>39078; 55388</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$garganta-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48,87%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>69,87%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>59,5%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>51,74%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,66%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,1; 87,4</t>
+          <t>23,85; 73,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,06; 78,04</t>
+          <t>13,1; 64,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,45; 80,12</t>
+          <t>12,49; 78,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,09; 70,44</t>
+          <t>46,42; 88,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,19; 65,15</t>
+          <t>37,85; 77,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,73; 82,18</t>
+          <t>22,5; 81,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,66; 74,74</t>
+          <t>41,15; 75,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,76; 66,88</t>
+          <t>34,18; 67,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,56; 71,17</t>
+          <t>29,49; 70,8</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>50,85%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>31,43%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>41,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>46,85%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>41,55%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>50,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>31,43%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>52,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,94; 63,36</t>
+          <t>30,01; 71,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,9; 65,3</t>
+          <t>13,26; 57,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,37; 58,94</t>
+          <t>32,77; 73,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,41; 71,09</t>
+          <t>20,65; 62,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 56,29</t>
+          <t>29,15; 65,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,41; 70,85</t>
+          <t>26,45; 59,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,14; 60,91</t>
+          <t>32,83; 60,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,31; 54,71</t>
+          <t>26,85; 54,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,32; 60,16</t>
+          <t>34,07; 59,87</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>35,64%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>60,53%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36,97%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>50,15%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>52,91%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>63,63%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>60,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,62; 69,93</t>
+          <t>13,24; 66,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,57; 75,52</t>
+          <t>40,71; 78,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,25; 83,65</t>
+          <t>19,72; 58,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,73; 66,69</t>
+          <t>28,19; 70,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,06; 77,7</t>
+          <t>28,19; 75,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,63; 55,12</t>
+          <t>41,84; 84,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,94; 61,55</t>
+          <t>27,98; 62,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,61; 71,71</t>
+          <t>43,22; 73,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,82; 64,4</t>
+          <t>32,43; 63,03</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>48,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47,02%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>67,76%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>46,54%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>35,85%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,46; 90,5</t>
+          <t>23,93; 73,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,9; 69,56</t>
+          <t>33,59; 70,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 57,28</t>
+          <t>21,75; 74,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,12; 73,32</t>
+          <t>33,25; 90,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,96; 71,1</t>
+          <t>25,91; 66,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,3; 77,53</t>
+          <t>15,46; 57,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,18; 76,29</t>
+          <t>34,73; 75,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,03; 64,88</t>
+          <t>35,06; 64,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,42; 57,91</t>
+          <t>25,15; 61,38</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>47,09%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>55,95%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>51,24%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>46,35%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>46,5%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,04; 68,12</t>
+          <t>35,85; 58,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,12; 62,33</t>
+          <t>38,07; 58,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,33; 56,94</t>
+          <t>33,32; 57,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,93; 58,05</t>
+          <t>43,51; 67,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,04; 57,26</t>
+          <t>41,82; 62,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,87; 57,08</t>
+          <t>35,69; 57,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,1; 60,09</t>
+          <t>42,54; 58,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,14; 56,39</t>
+          <t>41,96; 56,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37,95; 53,78</t>
+          <t>38,2; 53,8</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5493</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3539</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3478</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>8553</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>10199</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4590</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5493</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3539</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3478</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5153; 10699</t>
+          <t>2811; 8682</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6353; 13378</t>
+          <t>1338; 6543</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2080; 7108</t>
+          <t>889; 5568</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2722; 8303</t>
+          <t>5682; 10847</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1347; 6652</t>
+          <t>6488; 13312</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1049; 5850</t>
+          <t>1996; 7216</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10010; 17958</t>
+          <t>9887; 18121</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9235; 18295</t>
+          <t>9350; 18500</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4407; 11382</t>
+          <t>4715; 11321</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8088</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4991</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8988</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8424</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4440</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8088</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2532; 7662</t>
+          <t>4845; 11555</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5736; 12526</t>
+          <t>1873; 8147</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4942; 11949</t>
+          <t>5098; 11413</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5233; 11478</t>
+          <t>2498; 7516</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1990; 7952</t>
+          <t>5591; 12491</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4731; 11022</t>
+          <t>5363; 12091</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9076; 17200</t>
+          <t>9271; 17103</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9096; 18222</t>
+          <t>8944; 18056</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12295; 21555</t>
+          <t>12209; 21453</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2950</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10965</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5894</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>6368</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>4982</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7377</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2950</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10965</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5894</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3380; 8879</t>
+          <t>1096; 5512</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2502; 7111</t>
+          <t>7376; 14248</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4550; 9698</t>
+          <t>3144; 9335</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>971; 5520</t>
+          <t>3580; 8944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7621; 14076</t>
+          <t>2655; 7072</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2651; 8788</t>
+          <t>4851; 9740</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6069; 12910</t>
+          <t>5869; 13029</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11731; 19743</t>
+          <t>11899; 20186</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9314; 17733</t>
+          <t>8929; 17356</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5063</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10984</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4344</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>4638</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>7237</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5157</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5063</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10984</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4344</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2222; 6195</t>
+          <t>2512; 7718</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3716; 10818</t>
+          <t>7090; 14868</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2390; 8240</t>
+          <t>2010; 6924</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2426; 7695</t>
+          <t>2276; 6173</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6745; 15005</t>
+          <t>4029; 10346</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2060; 7164</t>
+          <t>2224; 8230</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6274; 13229</t>
+          <t>6022; 13108</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13575; 23782</t>
+          <t>12853; 23531</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5769; 13683</t>
+          <t>5942; 14503</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29929</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21805</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>24550</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>31407</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>25548</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21716</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>29929</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21805</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19323; 29890</t>
+          <t>16742; 27521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25203; 38201</t>
+          <t>24197; 37194</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20027; 31390</t>
+          <t>15946; 27450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15846; 27115</t>
+          <t>19092; 29770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22908; 36394</t>
+          <t>25632; 38324</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16210; 27319</t>
+          <t>19674; 31540</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39041; 54428</t>
+          <t>38531; 53426</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52614; 70406</t>
+          <t>52393; 70713</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39078; 55388</t>
+          <t>39342; 55408</t>
         </is>
       </c>
     </row>
